--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/Org_rev2_best/DHTCUN+50T+50EP+optim_purn/params_vs_psnr_analysis/DHTCUN_baseline_hutcn_hyperopt_study_3cols.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/Org_rev2_best/DHTCUN+50T+50EP+optim_purn/params_vs_psnr_analysis/DHTCUN_baseline_hutcn_hyperopt_study_3cols.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>FLOPs (G) @ 48x48</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>PSNR (dB)</t>
         </is>
       </c>
@@ -453,6 +458,9 @@
         <v>1016236</v>
       </c>
       <c r="C2" t="n">
+        <v>2.718208332</v>
+      </c>
+      <c r="D2" t="n">
         <v>26.83783912658691</v>
       </c>
     </row>
@@ -464,6 +472,9 @@
         <v>1251836</v>
       </c>
       <c r="C3" t="n">
+        <v>3.789107532</v>
+      </c>
+      <c r="D3" t="n">
         <v>26.01563720703125</v>
       </c>
     </row>
@@ -475,6 +486,9 @@
         <v>1168008</v>
       </c>
       <c r="C4" t="n">
+        <v>3.321879984</v>
+      </c>
+      <c r="D4" t="n">
         <v>28.65984687805176</v>
       </c>
     </row>
@@ -486,6 +500,9 @@
         <v>4114476</v>
       </c>
       <c r="C5" t="n">
+        <v>12.045350592</v>
+      </c>
+      <c r="D5" t="n">
         <v>27.24328155517578</v>
       </c>
     </row>
@@ -497,6 +514,9 @@
         <v>2390208</v>
       </c>
       <c r="C6" t="n">
+        <v>5.45183352</v>
+      </c>
+      <c r="D6" t="n">
         <v>26.10691719055176</v>
       </c>
     </row>
@@ -508,6 +528,9 @@
         <v>2948428</v>
       </c>
       <c r="C7" t="n">
+        <v>7.179103404</v>
+      </c>
+      <c r="D7" t="n">
         <v>28.00007972717285</v>
       </c>
     </row>
@@ -519,6 +542,9 @@
         <v>1278876</v>
       </c>
       <c r="C8" t="n">
+        <v>3.014963532</v>
+      </c>
+      <c r="D8" t="n">
         <v>28.01357231140137</v>
       </c>
     </row>
@@ -530,6 +556,9 @@
         <v>2467416</v>
       </c>
       <c r="C9" t="n">
+        <v>5.8936491</v>
+      </c>
+      <c r="D9" t="n">
         <v>30.67520637512207</v>
       </c>
     </row>
@@ -541,6 +570,9 @@
         <v>1038368</v>
       </c>
       <c r="C10" t="n">
+        <v>3.169263024</v>
+      </c>
+      <c r="D10" t="n">
         <v>27.81236763000488</v>
       </c>
     </row>
@@ -552,6 +584,9 @@
         <v>2606256</v>
       </c>
       <c r="C11" t="n">
+        <v>7.62551982</v>
+      </c>
+      <c r="D11" t="n">
         <v>28.01769943237305</v>
       </c>
     </row>
@@ -563,6 +598,9 @@
         <v>333796</v>
       </c>
       <c r="C12" t="n">
+        <v>0.7739107200000001</v>
+      </c>
+      <c r="D12" t="n">
         <v>30.04224357604981</v>
       </c>
     </row>
@@ -574,6 +612,9 @@
         <v>333796</v>
       </c>
       <c r="C13" t="n">
+        <v>0.7739107200000001</v>
+      </c>
+      <c r="D13" t="n">
         <v>30.10458297729492</v>
       </c>
     </row>
@@ -585,6 +626,9 @@
         <v>1587036</v>
       </c>
       <c r="C14" t="n">
+        <v>3.46504878</v>
+      </c>
+      <c r="D14" t="n">
         <v>30.14191131591797</v>
       </c>
     </row>
@@ -596,6 +640,9 @@
         <v>2389116</v>
       </c>
       <c r="C15" t="n">
+        <v>5.71449006</v>
+      </c>
+      <c r="D15" t="n">
         <v>30.26673736572265</v>
       </c>
     </row>
@@ -607,6 +654,9 @@
         <v>2389116</v>
       </c>
       <c r="C16" t="n">
+        <v>5.71449006</v>
+      </c>
+      <c r="D16" t="n">
         <v>29.63857574462891</v>
       </c>
     </row>
@@ -618,6 +668,9 @@
         <v>3658888</v>
       </c>
       <c r="C17" t="n">
+        <v>9.299889324</v>
+      </c>
+      <c r="D17" t="n">
         <v>30.41717414855957</v>
       </c>
     </row>
@@ -629,6 +682,9 @@
         <v>4739616</v>
       </c>
       <c r="C18" t="n">
+        <v>11.833013952</v>
+      </c>
+      <c r="D18" t="n">
         <v>30.07740440368652</v>
       </c>
     </row>
@@ -640,6 +696,9 @@
         <v>3775708</v>
       </c>
       <c r="C19" t="n">
+        <v>9.567521964000001</v>
+      </c>
+      <c r="D19" t="n">
         <v>30.40658302307129</v>
       </c>
     </row>
@@ -651,6 +710,9 @@
         <v>3658888</v>
       </c>
       <c r="C20" t="n">
+        <v>9.299889324</v>
+      </c>
+      <c r="D20" t="n">
         <v>30.47558250427246</v>
       </c>
     </row>
@@ -662,6 +724,9 @@
         <v>3148768</v>
       </c>
       <c r="C21" t="n">
+        <v>8.065491120000001</v>
+      </c>
+      <c r="D21" t="n">
         <v>30.56182022094726</v>
       </c>
     </row>
@@ -673,6 +738,9 @@
         <v>3148768</v>
       </c>
       <c r="C22" t="n">
+        <v>8.065491120000001</v>
+      </c>
+      <c r="D22" t="n">
         <v>30.61565399169922</v>
       </c>
     </row>
@@ -684,6 +752,9 @@
         <v>3148768</v>
       </c>
       <c r="C23" t="n">
+        <v>8.065491120000001</v>
+      </c>
+      <c r="D23" t="n">
         <v>30.60100364685059</v>
       </c>
     </row>
@@ -695,6 +766,9 @@
         <v>2133952</v>
       </c>
       <c r="C24" t="n">
+        <v>5.582340864</v>
+      </c>
+      <c r="D24" t="n">
         <v>30.49831085205078</v>
       </c>
     </row>
@@ -706,6 +780,9 @@
         <v>2585648</v>
       </c>
       <c r="C25" t="n">
+        <v>6.33656952</v>
+      </c>
+      <c r="D25" t="n">
         <v>30.52768745422363</v>
       </c>
     </row>
@@ -717,6 +794,9 @@
         <v>2133952</v>
       </c>
       <c r="C26" t="n">
+        <v>5.582340864</v>
+      </c>
+      <c r="D26" t="n">
         <v>30.47917823791504</v>
       </c>
     </row>
@@ -728,6 +808,9 @@
         <v>2585648</v>
       </c>
       <c r="C27" t="n">
+        <v>6.33656952</v>
+      </c>
+      <c r="D27" t="n">
         <v>30.56425323486328</v>
       </c>
     </row>
@@ -739,6 +822,9 @@
         <v>3181888</v>
       </c>
       <c r="C28" t="n">
+        <v>8.28667512</v>
+      </c>
+      <c r="D28" t="n">
         <v>30.67307929992676</v>
       </c>
     </row>
@@ -750,6 +836,9 @@
         <v>3181888</v>
       </c>
       <c r="C29" t="n">
+        <v>8.28667512</v>
+      </c>
+      <c r="D29" t="n">
         <v>30.66827926635742</v>
       </c>
     </row>
@@ -761,6 +850,9 @@
         <v>3181888</v>
       </c>
       <c r="C30" t="n">
+        <v>8.28667512</v>
+      </c>
+      <c r="D30" t="n">
         <v>30.80440101623535</v>
       </c>
     </row>
@@ -772,6 +864,9 @@
         <v>3829048</v>
       </c>
       <c r="C31" t="n">
+        <v>9.835154604</v>
+      </c>
+      <c r="D31" t="n">
         <v>30.74985580444336</v>
       </c>
     </row>
@@ -783,6 +878,9 @@
         <v>3880888</v>
       </c>
       <c r="C32" t="n">
+        <v>11.197648044</v>
+      </c>
+      <c r="D32" t="n">
         <v>30.77203903198242</v>
       </c>
     </row>
@@ -794,6 +892,9 @@
         <v>3174308</v>
       </c>
       <c r="C33" t="n">
+        <v>8.622697644</v>
+      </c>
+      <c r="D33" t="n">
         <v>30.6412036895752</v>
       </c>
     </row>
@@ -805,6 +906,9 @@
         <v>3145408</v>
       </c>
       <c r="C34" t="n">
+        <v>7.40193912</v>
+      </c>
+      <c r="D34" t="n">
         <v>30.64308013916015</v>
       </c>
     </row>
@@ -816,6 +920,9 @@
         <v>3233728</v>
       </c>
       <c r="C35" t="n">
+        <v>9.52530552</v>
+      </c>
+      <c r="D35" t="n">
         <v>30.74884223937988</v>
       </c>
     </row>
@@ -827,6 +934,9 @@
         <v>3880888</v>
       </c>
       <c r="C36" t="n">
+        <v>11.197648044</v>
+      </c>
+      <c r="D36" t="n">
         <v>30.76295967102051</v>
       </c>
     </row>
